--- a/consent_forms/036_physical_activity_readiness_and_consent_form--consent_forms.xlsx
+++ b/consent_forms/036_physical_activity_readiness_and_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,64 +520,76 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_1</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>A thorough medical history form will help identify any pre-existing conditions that may affect the physical activity.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please fill out this form to provide a comprehensive medical history.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_2</t>
+          <t>physical_activity_level</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your current level of physical activity?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one of the options below.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_3</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Do you have any of the following medical conditions?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select multiple conditions that apply.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,133 +601,153 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_4</t>
+          <t>current_medications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Please list your current medications.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List all your current medications.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_5</t>
+          <t>physical_activity_limitations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 5</t>
+          <t>What are your physical activity limitations?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_6</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 6</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Who is your emergency contact?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide contact information for your emergency contact.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_7</t>
+          <t>physical_activity_plan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 7</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Describe your plan for physical activity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select one of the options below.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_8</t>
+          <t>physical_activity_risk_assessment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Consent Form 8</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you have any physical activity risks?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select multiple risks that apply.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent</t>
+          <t>physical_activity_precautions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have any physical activity precautions?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select multiple precautions that apply.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +759,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent</t>
+          <t>physical_activity_goals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Concent</t>
+          <t>What are your physical activity goals?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent</t>
+          <t>physical_activity_schedule</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your physical activity schedule?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide the date for your physical activity schedule.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,294 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent</t>
+          <t>physical_activity_progress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>How will you track your physical activity progress?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select one of the options below.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>physical_activity_readiness_and_concent</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Physical Activity Readiness And Concent</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1078,9 +842,9 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,306 +867,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_5_choices</t>
+          <t>physical_activity_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>light_(less_than_30_minutes_a_day)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Light (less than 30 minutes a day)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_5_choices</t>
+          <t>physical_activity_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>moderate_(30-60_minutes_a_day)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Moderate (30-60 minutes a day)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_6_choices</t>
+          <t>physical_activity_level_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high_(more_than_60_minutes_a_day)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High (more than 60 minutes a day)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_consent_form_6_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>heart_condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Heart condition</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High blood pressure</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_plan_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_plan_to_do_light_physical_activity_(less_than_30_minutes_a_day)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I plan to do light physical activity (less than 30 minutes a day)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_plan_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_plan_to_do_moderate_physical_activity_(30-60_minutes_a_day)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I plan to do moderate physical activity (30-60 minutes a day)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_plan_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_plan_to_do_high-intensity_physical_activity_(more_than_60_minutes_a_day)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I plan to do high-intensity physical activity (more than 60 minutes a day)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_risk_assessment_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>risk_of_falls</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Risk of falls</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_risk_assessment_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>risk_of_overexertion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Risk of overexertion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_risk_assessment_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>risk_of_injury</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Risk of injury</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_precautions_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>precaution_for_knee_or_ankle_injuries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Precaution for knee or ankle injuries</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_precautions_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>precaution_for_heart_conditions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Precaution for heart conditions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_precautions_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>precaution_for_breathing_difficulties</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Precaution for breathing difficulties</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_progress_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_will_track_my_progress_daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I will track my progress daily</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_progress_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_will_track_my_progress_weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I will track my progress weekly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>physical_activity_readiness_and_concent_choices</t>
+          <t>physical_activity_progress_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_will_track_my_progress_monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I will track my progress monthly</t>
         </is>
       </c>
     </row>
